--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-08-26).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-08-26).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-182</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>R$ 773.259,32</t>
-  </si>
-  <si>
-    <t>R$ 3.985,87
-R$ 4.064,76</t>
-  </si>
-  <si>
-    <t>(0.8%)
-1.2%</t>
-  </si>
-  <si>
-    <t>44.0</t>
+185</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>R$ 780.683,68</t>
+  </si>
+  <si>
+    <t>R$ 3.962,86
+R$ 4.038,98</t>
+  </si>
+  <si>
+    <t>(0.9%)
+1.0%</t>
+  </si>
+  <si>
+    <t>43.7</t>
   </si>
   <si>
     <t>(8.1%)</t>
   </si>
   <si>
-    <t>37.3%</t>
-  </si>
-  <si>
-    <t>(3.3%)</t>
+    <t>35.3%</t>
+  </si>
+  <si>
+    <t>(5.2%)</t>
   </si>
   <si>
     <t>4.1%</t>
@@ -953,13 +953,13 @@
     <t>73.7%</t>
   </si>
   <si>
-    <t>6.9%</t>
+    <t>7.0%</t>
   </si>
   <si>
     <t>4.4</t>
   </si>
   <si>
-    <t>6.4</t>
+    <t>6.5</t>
   </si>
   <si>
     <t>10.9</t>
@@ -968,13 +968,13 @@
     <t>17.6</t>
   </si>
   <si>
-    <t>75.4%</t>
+    <t>75.3%</t>
   </si>
   <si>
     <t>-R$ 24.548,83</t>
   </si>
   <si>
-    <t>2.95</t>
+    <t>2.94</t>
   </si>
   <si>
     <t>3.52</t>
@@ -5994,7 +5994,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -6030,25 +6030,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>3357.6500000000001</v>
+      </c>
+      <c r="P36" s="5">
+        <v>3357.6500000000001</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.18562762185906578</v>
+      </c>
+      <c r="R36" s="7">
+        <v>39</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.14705882352941169</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.29047092460500645</v>
+      </c>
+      <c r="U36" s="6">
+        <v>-0.016285288818072164</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.15371703423525382</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.095890876059148519</v>
+      </c>
+      <c r="X36" s="8">
+        <v>26.590578260869567</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.043478260869565216</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>4.5315324324324324</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>5.4289869565217392</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>10.347099999999999</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>17.302173913043479</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.73913043478260865</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -7913,7 +7949,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7949,25 +7985,61 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
-      <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="O51" s="5">
+        <v>1031.8699999999999</v>
+      </c>
+      <c r="P51" s="5">
+        <v>1031.8699999999999</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>2.7880690161527166</v>
+      </c>
+      <c r="R51" s="7">
+        <v>8</v>
+      </c>
+      <c r="S51" s="6">
+        <v>1.6666666666666665</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.29325399517381073</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.020819483074418291</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.10323684185023309</v>
+      </c>
+      <c r="X51" s="8">
+        <v>26.125</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>3.4125000000000001</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>12.086116666666667</v>
+      </c>
+      <c r="AC51" s="8">
+        <v>15.308332999999999</v>
+      </c>
+      <c r="AD51" s="8">
+        <v>22.230549999999997</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -12672,7 +12744,7 @@
         <v>0</v>
       </c>
       <c r="AH88" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI88" s="11"/>
       <c r="AJ88" s="13">
@@ -12711,7 +12783,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12745,25 +12817,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>3034.8400000000001</v>
+      </c>
+      <c r="P89" s="5">
+        <v>3034.8400000000001</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.46184578009877031</v>
+      </c>
+      <c r="R89" s="7">
+        <v>32</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.41818181818181821</v>
+      </c>
+      <c r="T89" s="6">
+        <v>-4.5625352901635665</v>
+      </c>
+      <c r="U89" s="6">
+        <v>-4.8705416430520225</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.036547890498345878</v>
+      </c>
+      <c r="W89" s="6">
+        <v>0.0021375097204465471</v>
+      </c>
+      <c r="X89" s="8">
+        <v>34.599999999999994</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>5.2546875000000002</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>12.162747058823529</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>25.190738888888887</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.3888888888888889</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -16823,7 +16929,7 @@
         <v>-103.8</v>
       </c>
       <c r="AH121" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI121" s="11"/>
       <c r="AJ121" s="13">
@@ -17085,7 +17191,7 @@
         <v>0</v>
       </c>
       <c r="AH123" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI123" s="11"/>
       <c r="AJ123" s="13">
@@ -17478,7 +17584,7 @@
         <v>0</v>
       </c>
       <c r="AH126" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI126" s="11"/>
       <c r="AJ126" s="13">
@@ -18655,7 +18761,7 @@
         <v>-161.69999999999999</v>
       </c>
       <c r="AH135" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI135" s="11"/>
       <c r="AJ135" s="13">
@@ -18786,7 +18892,7 @@
         <v>0</v>
       </c>
       <c r="AH136" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI136" s="11"/>
       <c r="AJ136" s="13">
@@ -20969,7 +21075,7 @@
         <v>-176.22999999999999</v>
       </c>
       <c r="AH153" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AI153" s="11"/>
       <c r="AJ153" s="13">
@@ -21096,7 +21202,7 @@
         <v>-2.5499999999999998</v>
       </c>
       <c r="AH154" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI154" s="11"/>
       <c r="AJ154" s="13">
@@ -22253,7 +22359,7 @@
         <v>0</v>
       </c>
       <c r="AH163" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI163" s="11"/>
       <c r="AJ163" s="13">
@@ -28418,7 +28524,7 @@
       <c r="AF212" s="9"/>
       <c r="AG212" s="5"/>
       <c r="AH212" s="10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI212" s="11"/>
       <c r="AJ212" s="12"/>
